--- a/Reporte-Calificaciones-Junio2026.xlsx
+++ b/Reporte-Calificaciones-Junio2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0117D12D-110C-4F7C-9A58-AC171003CBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{0117D12D-110C-4F7C-9A58-AC171003CBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1102C5EB-88EB-45EB-929B-DFA22165951F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11772" windowHeight="12240" xr2:uid="{78ED0044-83E2-4F2D-B233-224FE08F0EAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{78ED0044-83E2-4F2D-B233-224FE08F0EAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>REPORTE DE CALIFICACIONES - JUNIO 2026</t>
   </si>
@@ -100,6 +100,45 @@
   </si>
   <si>
     <t xml:space="preserve">Total Reprobados </t>
+  </si>
+  <si>
+    <r>
+      <t>¿Qué es IF?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Es una fórmula que toma una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>decisión</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> basada en una condición.</t>
+    </r>
+  </si>
+  <si>
+    <t>Si esto es verdad → haz esto, sino → haz esto otro</t>
   </si>
 </sst>
 </file>
@@ -185,16 +224,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1416,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3091B607-BD9C-4AC8-8A65-0A93959285B3}">
-  <dimension ref="A2:F19"/>
+  <dimension ref="A2:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1425,17 +1473,17 @@
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1449,7 +1497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1463,7 +1511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1479,7 +1527,7 @@
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1495,7 +1543,7 @@
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1507,11 +1555,11 @@
         <v>APROBADO</v>
       </c>
       <c r="D7" s="2" t="str">
-        <f>IF(B7&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" ref="D7:D12" si="1">IF(B7&gt;=90, "TIENE BECA", "SIN BECA")</f>
         <v>TIENE BECA</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1523,11 +1571,11 @@
         <v>REPROBADO</v>
       </c>
       <c r="D8" s="2" t="str">
-        <f>IF(B8&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" si="1"/>
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
@@ -1539,11 +1587,11 @@
         <v>APROBADO</v>
       </c>
       <c r="D9" s="2" t="str">
-        <f>IF(B9&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" si="1"/>
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1555,11 +1603,11 @@
         <v>APROBADO</v>
       </c>
       <c r="D10" s="2" t="str">
-        <f>IF(B10&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" si="1"/>
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1571,11 +1619,11 @@
         <v>REPROBADO</v>
       </c>
       <c r="D11" s="2" t="str">
-        <f>IF(B11&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" si="1"/>
         <v>SIN BECA</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
@@ -1587,19 +1635,19 @@
         <v>APROBADO</v>
       </c>
       <c r="D12" s="2" t="str">
-        <f>IF(B12&gt;=90, "TIENE BECA", "SIN BECA")</f>
+        <f t="shared" si="1"/>
         <v>TIENE BECA</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1608,7 +1656,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1616,8 +1664,17 @@
         <f>MIN(B5:B12)</f>
         <v>35</v>
       </c>
+      <c r="F16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1625,8 +1682,9 @@
         <f>AVERAGE(B5:B12)</f>
         <v>68.125</v>
       </c>
+      <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
@@ -1634,8 +1692,16 @@
         <f>COUNTIF(C5:C12, "APROBADO")</f>
         <v>5</v>
       </c>
+      <c r="F18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1645,8 +1711,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="F18:K18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Reporte-Calificaciones-Junio2026.xlsx
+++ b/Reporte-Calificaciones-Junio2026.xlsx
@@ -231,11 +231,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1474,14 +1474,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1682,7 +1682,7 @@
         <f>AVERAGE(B5:B12)</f>
         <v>68.125</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
